--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92565947346</v>
+        <v>46157.93091715503</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93091715503</v>
+        <v>46157.93168549888</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93168549888</v>
+        <v>46157.93397885868</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93397885868</v>
+        <v>46157.93715641153</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93715641153</v>
+        <v>46158.28214277258</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214277258</v>
+        <v>46158.29675661558</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675661558</v>
+        <v>46158.29812344276</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812344276</v>
+        <v>46158.33385210903</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385210903</v>
+        <v>46158.36854923353</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36854923353</v>
+        <v>46158.37285711071</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
